--- a/CobbDocs/CobbBOCYearInReview_data.xlsx
+++ b/CobbDocs/CobbBOCYearInReview_data.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jcbra\GitHub\This-One-Will-Be-Different\CobbDocs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72D8FA25-C842-42BA-909B-95C908B91C72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB6A9AF3-BFB0-4FCC-884B-AB85F23AB17D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{CEDEA0C4-ED09-4EF5-AB2D-04585F13BFFE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CEDEA0C4-ED09-4EF5-AB2D-04585F13BFFE}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sources for Table 13.2" sheetId="1" r:id="rId1"/>
-    <sheet name="Sources for Table 21.6" sheetId="2" r:id="rId2"/>
+    <sheet name="README" sheetId="5" r:id="rId1"/>
+    <sheet name="Table 13.2 sources" sheetId="1" r:id="rId2"/>
+    <sheet name="Table 26.1 sources" sheetId="2" r:id="rId3"/>
+    <sheet name="Table 26.2 sources" sheetId="3" r:id="rId4"/>
+    <sheet name="Table 26.2 (2024 worksheet)" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="142">
   <si>
     <t>Sales Taxes</t>
   </si>
@@ -261,9 +264,6 @@
     <t>non-gen fund</t>
   </si>
   <si>
-    <t>Revenue from Taxes (-- ANLBC Rent and isurance)</t>
-  </si>
-  <si>
     <t>Slide 6</t>
   </si>
   <si>
@@ -291,9 +291,6 @@
     <t>Total Cost (removing insurance)</t>
   </si>
   <si>
-    <t>2021 and 2022 General Fund contributions don't make much sense, and unclear what they reflect. Therefore, This estimate GF by substracting all other revenue from Total Revenue</t>
-  </si>
-  <si>
     <t>NOTES</t>
   </si>
   <si>
@@ -303,9 +300,6 @@
     <t>Non-debt service costs (removing insurance)</t>
   </si>
   <si>
-    <t>I decided to remove the insurance revenue and cost components in the book version for similicity, because they cancel out. They remain here. See below for totals without insurance.</t>
-  </si>
-  <si>
     <t>It reports whole dollar amounts, not in millions like the book table.</t>
   </si>
   <si>
@@ -324,9 +318,6 @@
     <t>Expenditures</t>
   </si>
   <si>
-    <t>Avearage yearly contribution</t>
-  </si>
-  <si>
     <t>(from 2017 slide deck)</t>
   </si>
   <si>
@@ -334,17 +325,159 @@
   </si>
   <si>
     <t>Proposed 2015</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2015 Projections </t>
+  </si>
+  <si>
+    <t>Annual Debt Service</t>
+  </si>
+  <si>
+    <t>Funding Breakdown</t>
+  </si>
+  <si>
+    <t>Hotel Motel Tax</t>
+  </si>
+  <si>
+    <t>Property Tax – General Fund</t>
+  </si>
+  <si>
+    <t>Property Tax - CSSDII</t>
+  </si>
+  <si>
+    <t>$3.00 Per Room Night Fee – CSSDI</t>
+  </si>
+  <si>
+    <t>Rental Car Tax</t>
+  </si>
+  <si>
+    <t>Total County</t>
+  </si>
+  <si>
+    <t>Annual Braves Rent Requirement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">General Fund Property Tax – </t>
+  </si>
+  <si>
+    <t>Paid by Battery Properties</t>
+  </si>
+  <si>
+    <t>Graph from CobbBOCYearInReview_2023.pdf</t>
+  </si>
+  <si>
+    <t>Not included in following year's presentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Cumberland SSD  I (Hotel)</t>
+  </si>
+  <si>
+    <t>Slide 5 Amount to stadium after taking out circulator fee. The sum total is on Slide 2, which creates odd "surplus"</t>
+  </si>
+  <si>
+    <t>Counts all revenue from SSD Hotel</t>
+  </si>
+  <si>
+    <t>Non GF Taxes</t>
+  </si>
+  <si>
+    <t>Braves</t>
+  </si>
+  <si>
+    <t>Debt service</t>
+  </si>
+  <si>
+    <t>Difference</t>
+  </si>
+  <si>
+    <t>Braves + NonGF</t>
+  </si>
+  <si>
+    <t>Amount from GF going toward debt service</t>
+  </si>
+  <si>
+    <t>This surplus is the difference of tax revenue collected from no GF sources, in comparison to DS</t>
+  </si>
+  <si>
+    <t>Non DS costs</t>
+  </si>
+  <si>
+    <t>DS + Non-DS</t>
+  </si>
+  <si>
+    <t>Gen Fund</t>
+  </si>
+  <si>
+    <t>After crediting all SSD Hotel toward DS</t>
+  </si>
+  <si>
+    <t>Braves GF portion</t>
+  </si>
+  <si>
+    <t>Surplus after Braves GF to DS</t>
+  </si>
+  <si>
+    <t>See Sources for Table 21.6</t>
+  </si>
+  <si>
+    <t>Notes on  CobbBOCYearInReview_2024.pdf</t>
+  </si>
+  <si>
+    <t>This Excel file provides the cost and revenue figures that I collected from CobbBOCYearInReview slide decks in this folder. It includes source locations (slide) and formulas for calculations.</t>
+  </si>
+  <si>
+    <t>&lt;== See Table 26.2 (2024 worksheet)</t>
+  </si>
+  <si>
+    <t>Data from various years. For example, see Slide 7 of  CobbBOCYearInReview_2023.pdf</t>
+  </si>
+  <si>
+    <t>&lt;== Erroneous reported accounting claiming a 1,096,608 positive contribution back to general fund. This can't happen. Correcting for this error results in a need to draw ~$600k from GF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Worksheet of how I extracted the GF component going toward debt service in 2024 in Table 26.2. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">The annual report uses some funky accounting, crediting some SSD Hotel revenue going to circulator (I think) back toward debt service, which creates an odd "negative" surplus of revenue. </t>
+  </si>
+  <si>
+    <t>Another 600K is needed out of GF to cover DS</t>
+  </si>
+  <si>
+    <t>Even if all hotel SSD revenue is credited to the stadium, $1.4 mill is still needed from GF to cove non DS costs</t>
+  </si>
+  <si>
+    <t>Only crediting non-circulator fee, as has been standard</t>
+  </si>
+  <si>
+    <t>I decided to remove the insurance revenue and cost components in the book version for simplicity, because they cancel out. They remain here. See below for totals without insurance.</t>
+  </si>
+  <si>
+    <t>2021 and 2022 General Fund contributions don't make much sense, and unclear what they reflect. Therefore, This estimate GF by subtracting all other revenue from Total Revenue</t>
+  </si>
+  <si>
+    <t>Revenue from Taxes (-- ANLBC Rent and insurance)</t>
+  </si>
+  <si>
+    <t>Average yearly contribution</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -385,6 +518,15 @@
       <color theme="1"/>
       <name val="Garamond"/>
       <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -436,7 +578,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -489,7 +631,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -498,6 +640,17 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -514,6 +667,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>132248</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>67275</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B26D013B-4E56-4A5A-9655-EC2571EAED59}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10500360" y="548640"/>
+          <a:ext cx="7447448" cy="5538435"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -832,6 +1034,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B679663-0F15-4013-919E-FBFB9B5174CA}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="59" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="46" t="s">
+        <v>129</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DB8A0A1-FC47-420C-8AAA-F232B26C0CDC}">
   <dimension ref="A1:M39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1137,6 +1357,9 @@
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C14" s="1" t="s">
+        <v>110</v>
+      </c>
       <c r="H14"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
@@ -1511,7 +1734,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DC757A5-9272-4B6E-A060-6E35B55AA6D9}">
   <dimension ref="A1:AD44"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1550,34 +1773,34 @@
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" s="31" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="35"/>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>88</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>84</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.3">
@@ -1588,10 +1811,10 @@
     <row r="8" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A8" s="26"/>
       <c r="B8" s="26" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C8" s="36" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D8" s="26"/>
       <c r="E8" s="26"/>
@@ -1639,7 +1862,7 @@
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="37"/>
@@ -2522,7 +2745,7 @@
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A24" s="16" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B24" s="13">
         <f>SUM(B10:B22)</f>
@@ -2600,7 +2823,7 @@
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
-        <v>74</v>
+        <v>140</v>
       </c>
       <c r="B25" s="13">
         <f>SUM(B10:B18)</f>
@@ -2693,7 +2916,7 @@
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B27" s="33"/>
       <c r="C27" s="37"/>
@@ -2768,21 +2991,21 @@
         <v>22484158</v>
       </c>
       <c r="T28" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U28" s="13"/>
       <c r="V28" s="13">
         <v>22486658</v>
       </c>
       <c r="W28" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="X28" s="13"/>
       <c r="Y28" s="13">
         <v>22483495</v>
       </c>
       <c r="Z28" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AA28" s="13"/>
       <c r="AB28" s="13"/>
@@ -2801,7 +3024,7 @@
         <v>1170000</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>95</v>
+        <v>141</v>
       </c>
       <c r="D29" s="10"/>
       <c r="E29" s="10"/>
@@ -2838,21 +3061,21 @@
         <v>1320000</v>
       </c>
       <c r="T29" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U29" s="13"/>
       <c r="V29" s="13">
         <v>1350000</v>
       </c>
       <c r="W29" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="X29" s="13"/>
       <c r="Y29" s="13">
         <v>1380000</v>
       </c>
       <c r="Z29" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AA29" s="13"/>
       <c r="AB29" s="13"/>
@@ -2860,7 +3083,7 @@
         <v>1410000</v>
       </c>
       <c r="AD29" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.3">
@@ -2908,21 +3131,21 @@
         <v>169655</v>
       </c>
       <c r="T30" s="14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="U30" s="13"/>
       <c r="V30" s="13">
         <v>169656</v>
       </c>
       <c r="W30" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="X30" s="13"/>
       <c r="Y30" s="13">
         <v>169656</v>
       </c>
       <c r="Z30" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AA30" s="13"/>
       <c r="AB30" s="13"/>
@@ -2930,7 +3153,7 @@
         <v>169656</v>
       </c>
       <c r="AD30" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.3">
@@ -2978,21 +3201,21 @@
         <v>71361</v>
       </c>
       <c r="T31" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U31" s="13"/>
       <c r="V31" s="13">
         <v>75000</v>
       </c>
       <c r="W31" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="X31" s="13"/>
       <c r="Y31" s="13">
         <v>75000</v>
       </c>
       <c r="Z31" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AA31" s="13"/>
       <c r="AB31" s="13"/>
@@ -3000,7 +3223,7 @@
         <v>80000</v>
       </c>
       <c r="AD31" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="32" spans="1:30" x14ac:dyDescent="0.3">
@@ -3044,21 +3267,21 @@
         <v>817867</v>
       </c>
       <c r="T32" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U32" s="13"/>
       <c r="V32" s="13">
         <v>925000</v>
       </c>
       <c r="W32" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="X32" s="13"/>
       <c r="Y32" s="13">
         <v>925000</v>
       </c>
       <c r="Z32" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AA32" s="13"/>
       <c r="AB32" s="13"/>
@@ -3066,7 +3289,7 @@
         <v>925000</v>
       </c>
       <c r="AD32" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:30" x14ac:dyDescent="0.3">
@@ -3163,7 +3386,7 @@
     </row>
     <row r="35" spans="1:30" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A35" s="19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B35" s="33"/>
       <c r="C35" s="20"/>
@@ -3279,7 +3502,7 @@
     </row>
     <row r="39" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B39" s="5">
         <f>SUM(B24-B21)</f>
@@ -3326,14 +3549,14 @@
     </row>
     <row r="40" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B40" s="5">
         <f>SUM(B34-B31)</f>
         <v>23839655</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F40" s="5">
         <f>SUM(F34-F31)</f>
@@ -3370,7 +3593,7 @@
     </row>
     <row r="42" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B42" s="30">
         <f>SUM(B18/B25)</f>
@@ -3411,7 +3634,7 @@
     </row>
     <row r="43" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B43" s="5">
         <f>SUM(B29+B30+B32)</f>
@@ -3452,11 +3675,796 @@
     </row>
     <row r="44" spans="1:30" ht="57.6" x14ac:dyDescent="0.3">
       <c r="W44" s="25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63A7A59E-8897-45FA-B481-AA56462226EE}">
+  <dimension ref="A1:L29"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="27.77734375" customWidth="1"/>
+    <col min="2" max="2" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.109375" customWidth="1"/>
+    <col min="9" max="9" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="33.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" s="45" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>131</v>
+      </c>
+      <c r="L2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C4">
+        <v>2018</v>
+      </c>
+      <c r="D4">
+        <v>2019</v>
+      </c>
+      <c r="E4">
+        <v>2020</v>
+      </c>
+      <c r="F4">
+        <v>2021</v>
+      </c>
+      <c r="G4">
+        <v>2022</v>
+      </c>
+      <c r="H4">
+        <v>2023</v>
+      </c>
+      <c r="I4">
+        <v>2024</v>
+      </c>
+      <c r="J4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B5" s="40">
+        <v>22500000</v>
+      </c>
+      <c r="C5" s="40">
+        <v>22484130</v>
+      </c>
+      <c r="D5" s="40">
+        <v>22485537</v>
+      </c>
+      <c r="E5" s="40">
+        <v>22484078</v>
+      </c>
+      <c r="F5" s="40">
+        <v>22484158</v>
+      </c>
+      <c r="G5" s="40">
+        <v>22486658</v>
+      </c>
+      <c r="H5" s="40">
+        <v>22483495</v>
+      </c>
+      <c r="I5" s="40">
+        <v>22487130</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="40">
+        <v>1510000</v>
+      </c>
+      <c r="C7" s="40">
+        <v>2742242</v>
+      </c>
+      <c r="D7" s="40">
+        <v>3027943</v>
+      </c>
+      <c r="E7" s="40">
+        <v>419036</v>
+      </c>
+      <c r="F7" s="40">
+        <v>865894</v>
+      </c>
+      <c r="G7" s="40">
+        <v>3451298</v>
+      </c>
+      <c r="H7" s="40">
+        <v>3869678</v>
+      </c>
+      <c r="I7" s="40">
+        <v>3847826</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>100</v>
+      </c>
+      <c r="B8" s="40">
+        <v>6400000</v>
+      </c>
+      <c r="C8" s="40">
+        <v>5301155</v>
+      </c>
+      <c r="D8" s="40">
+        <v>4416875</v>
+      </c>
+      <c r="E8" s="40">
+        <v>5039473</v>
+      </c>
+      <c r="F8" s="40">
+        <v>4862519</v>
+      </c>
+      <c r="G8" s="40">
+        <v>2129472</v>
+      </c>
+      <c r="H8" s="40">
+        <v>1751857</v>
+      </c>
+      <c r="I8" s="44">
+        <f>SUM('Table 26.2 (2024 worksheet)'!C15-'Table 26.2 (2024 worksheet)'!B15)</f>
+        <v>599645</v>
+      </c>
+      <c r="J8" s="43" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>101</v>
+      </c>
+      <c r="B9" s="40">
+        <v>5150000</v>
+      </c>
+      <c r="C9" s="40">
+        <v>5150000</v>
+      </c>
+      <c r="D9" s="40">
+        <v>6470000</v>
+      </c>
+      <c r="E9" s="40">
+        <v>9293021</v>
+      </c>
+      <c r="F9" s="40">
+        <v>8200000</v>
+      </c>
+      <c r="G9" s="40">
+        <v>8500000</v>
+      </c>
+      <c r="H9" s="40">
+        <v>7664669</v>
+      </c>
+      <c r="I9" s="40">
+        <v>8970865</v>
+      </c>
+      <c r="J9" s="43"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10" s="40">
+        <v>2740000</v>
+      </c>
+      <c r="C10" s="40">
+        <v>2534130</v>
+      </c>
+      <c r="D10" s="40">
+        <v>1600000</v>
+      </c>
+      <c r="E10" s="40">
+        <v>1025000</v>
+      </c>
+      <c r="F10" s="40">
+        <v>1800000</v>
+      </c>
+      <c r="G10" s="40">
+        <v>1500000</v>
+      </c>
+      <c r="H10" s="40">
+        <v>2274330</v>
+      </c>
+      <c r="I10" s="40">
+        <v>3936236</v>
+      </c>
+      <c r="J10" s="43"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>103</v>
+      </c>
+      <c r="B11" s="40">
+        <v>600000</v>
+      </c>
+      <c r="C11" s="40">
+        <v>656603</v>
+      </c>
+      <c r="D11" s="40">
+        <v>870719</v>
+      </c>
+      <c r="E11" s="40">
+        <v>607548</v>
+      </c>
+      <c r="F11" s="40">
+        <v>655745</v>
+      </c>
+      <c r="G11" s="40">
+        <v>805888</v>
+      </c>
+      <c r="H11" s="40">
+        <v>822961</v>
+      </c>
+      <c r="I11" s="40">
+        <v>728811</v>
+      </c>
+      <c r="J11" s="43"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B12" s="40">
+        <v>16400000</v>
+      </c>
+      <c r="C12" s="40">
+        <v>16384130</v>
+      </c>
+      <c r="D12" s="40">
+        <v>16385537</v>
+      </c>
+      <c r="E12" s="40">
+        <v>16384078</v>
+      </c>
+      <c r="F12" s="40">
+        <v>16384158</v>
+      </c>
+      <c r="G12" s="40">
+        <v>16386658</v>
+      </c>
+      <c r="H12" s="40">
+        <v>16383495</v>
+      </c>
+      <c r="I12" s="40">
+        <v>17483738</v>
+      </c>
+      <c r="J12" s="43"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>105</v>
+      </c>
+      <c r="B13" s="40">
+        <v>6100000</v>
+      </c>
+      <c r="C13" s="40">
+        <v>6100000</v>
+      </c>
+      <c r="D13" s="40">
+        <v>6100000</v>
+      </c>
+      <c r="E13" s="40">
+        <v>6100000</v>
+      </c>
+      <c r="F13" s="40">
+        <v>6100000</v>
+      </c>
+      <c r="G13" s="40">
+        <v>6100000</v>
+      </c>
+      <c r="H13" s="40">
+        <v>6100000</v>
+      </c>
+      <c r="I13" s="40">
+        <v>6100000</v>
+      </c>
+      <c r="J13" s="43"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>106</v>
+      </c>
+      <c r="B15" s="40">
+        <v>50724</v>
+      </c>
+      <c r="C15" s="40">
+        <v>1881802</v>
+      </c>
+      <c r="D15" s="40">
+        <v>1868937</v>
+      </c>
+      <c r="E15" s="40">
+        <v>1972895</v>
+      </c>
+      <c r="F15" s="40">
+        <v>2119549</v>
+      </c>
+      <c r="G15" s="40">
+        <v>2509272</v>
+      </c>
+      <c r="H15" s="40">
+        <v>2597469</v>
+      </c>
+      <c r="I15" s="40">
+        <v>1954115</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B18" s="40">
+        <f t="shared" ref="B18:F18" si="0">SUM(B8-B15)</f>
+        <v>6349276</v>
+      </c>
+      <c r="C18" s="40">
+        <f t="shared" si="0"/>
+        <v>3419353</v>
+      </c>
+      <c r="D18" s="40">
+        <f t="shared" si="0"/>
+        <v>2547938</v>
+      </c>
+      <c r="E18" s="40">
+        <f t="shared" si="0"/>
+        <v>3066578</v>
+      </c>
+      <c r="F18" s="40">
+        <f t="shared" si="0"/>
+        <v>2742970</v>
+      </c>
+      <c r="G18" s="40">
+        <f>SUM(G8-G15)</f>
+        <v>-379800</v>
+      </c>
+      <c r="H18" s="40">
+        <f>SUM(H8-H15)</f>
+        <v>-845612</v>
+      </c>
+      <c r="I18" s="40">
+        <f>SUM(I8-I15)</f>
+        <v>-1354470</v>
+      </c>
+      <c r="J18" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B19" s="41">
+        <f>SUM(B18/1000000)</f>
+        <v>6.3492759999999997</v>
+      </c>
+      <c r="C19" s="41">
+        <f t="shared" ref="C19:H19" si="1">SUM(C18/1000000)</f>
+        <v>3.4193530000000001</v>
+      </c>
+      <c r="D19" s="41">
+        <f t="shared" si="1"/>
+        <v>2.5479379999999998</v>
+      </c>
+      <c r="E19" s="41">
+        <f t="shared" si="1"/>
+        <v>3.0665779999999998</v>
+      </c>
+      <c r="F19" s="41">
+        <f t="shared" si="1"/>
+        <v>2.7429700000000001</v>
+      </c>
+      <c r="G19" s="41">
+        <f t="shared" si="1"/>
+        <v>-0.37980000000000003</v>
+      </c>
+      <c r="H19" s="41">
+        <f t="shared" si="1"/>
+        <v>-0.84561200000000003</v>
+      </c>
+      <c r="I19" s="41">
+        <f t="shared" ref="I19" si="2">SUM(I18/1000000)</f>
+        <v>-1.3544700000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J20" s="5"/>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J21" s="40"/>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J22" s="5"/>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B24" s="40"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="40"/>
+      <c r="I24" s="40"/>
+      <c r="J24" s="5"/>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B25" s="40"/>
+      <c r="C25" s="40"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="40"/>
+      <c r="G25" s="40"/>
+      <c r="H25" s="40"/>
+      <c r="I25" s="40"/>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="H27" s="40"/>
+      <c r="I27" s="40"/>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="H28" s="40"/>
+      <c r="I28" s="40"/>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="H29" s="40"/>
+      <c r="I29" s="40"/>
+      <c r="J29" s="40"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="J8:J13"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F217674-BED3-4481-AD18-C4FE36D8BACB}">
+  <dimension ref="A1:L25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="42.21875" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="19.109375" customWidth="1"/>
+    <col min="5" max="5" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.88671875" customWidth="1"/>
+    <col min="9" max="10" width="18.109375" customWidth="1"/>
+    <col min="11" max="11" width="10.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" s="31" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="42" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>135</v>
+      </c>
+      <c r="H4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>2024</v>
+      </c>
+      <c r="H5">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>111</v>
+      </c>
+      <c r="B6" s="5">
+        <v>2239983</v>
+      </c>
+      <c r="C6" t="s">
+        <v>112</v>
+      </c>
+      <c r="G6" t="s">
+        <v>111</v>
+      </c>
+      <c r="H6" s="5">
+        <v>3936236</v>
+      </c>
+      <c r="I6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="5">
+        <v>8970865</v>
+      </c>
+      <c r="G7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H7" s="5">
+        <v>8970865</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="5">
+        <v>3847826</v>
+      </c>
+      <c r="G8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H8" s="5">
+        <v>3847826</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="5">
+        <v>728811</v>
+      </c>
+      <c r="G9" t="s">
+        <v>58</v>
+      </c>
+      <c r="H9" s="5">
+        <v>728811</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>114</v>
+      </c>
+      <c r="B12" s="5">
+        <f>SUM(B6:B9)</f>
+        <v>15787485</v>
+      </c>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="G12" t="s">
+        <v>114</v>
+      </c>
+      <c r="H12" s="5">
+        <f>SUM(H6:H9)</f>
+        <v>17483738</v>
+      </c>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>115</v>
+      </c>
+      <c r="B13" s="5">
+        <v>6100000</v>
+      </c>
+      <c r="G13" t="s">
+        <v>115</v>
+      </c>
+      <c r="H13" s="5">
+        <v>6100000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C14" t="s">
+        <v>116</v>
+      </c>
+      <c r="E14" t="s">
+        <v>117</v>
+      </c>
+      <c r="I14" t="s">
+        <v>116</v>
+      </c>
+      <c r="K14" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>118</v>
+      </c>
+      <c r="B15" s="5">
+        <f>SUM(B12+B13)</f>
+        <v>21887485</v>
+      </c>
+      <c r="C15" s="5">
+        <v>22487130</v>
+      </c>
+      <c r="D15" s="5"/>
+      <c r="E15" s="44">
+        <f>SUM(C15-B15)</f>
+        <v>599645</v>
+      </c>
+      <c r="F15" t="s">
+        <v>119</v>
+      </c>
+      <c r="G15" t="s">
+        <v>118</v>
+      </c>
+      <c r="H15" s="5">
+        <f>SUM(H12+H13)</f>
+        <v>23583738</v>
+      </c>
+      <c r="I15" s="5">
+        <v>22487130</v>
+      </c>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5">
+        <f>SUM(I15-H15)</f>
+        <v>-1096608</v>
+      </c>
+      <c r="L15" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>121</v>
+      </c>
+      <c r="C17" s="5">
+        <v>2504656</v>
+      </c>
+      <c r="D17" t="s">
+        <v>127</v>
+      </c>
+      <c r="E17" s="5">
+        <f>SUM(C17+E15)</f>
+        <v>3104301</v>
+      </c>
+      <c r="H17" t="s">
+        <v>121</v>
+      </c>
+      <c r="I17" s="5">
+        <v>2504656</v>
+      </c>
+      <c r="J17" t="s">
+        <v>127</v>
+      </c>
+      <c r="K17" s="5">
+        <f>SUM(I17+K15)</f>
+        <v>1408048</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B18" s="5"/>
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B19" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C19" s="5">
+        <f>SUM(C15+C17)</f>
+        <v>24991786</v>
+      </c>
+      <c r="D19" s="5"/>
+      <c r="H19" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="I19" s="5">
+        <f>SUM(I15+I17)</f>
+        <v>24991786</v>
+      </c>
+      <c r="J19" s="5"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>123</v>
+      </c>
+      <c r="B21" s="44">
+        <f>SUM(C19-B15)</f>
+        <v>3104301</v>
+      </c>
+      <c r="C21" t="s">
+        <v>137</v>
+      </c>
+      <c r="G21" t="s">
+        <v>123</v>
+      </c>
+      <c r="H21" s="44">
+        <f>SUM(I19-H15)</f>
+        <v>1408048</v>
+      </c>
+      <c r="I21" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>125</v>
+      </c>
+      <c r="B24" s="5">
+        <v>1954115</v>
+      </c>
+      <c r="C24" t="s">
+        <v>50</v>
+      </c>
+      <c r="G24" t="s">
+        <v>125</v>
+      </c>
+      <c r="H24" s="5">
+        <v>1954115</v>
+      </c>
+      <c r="I24" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>126</v>
+      </c>
+      <c r="B25" s="44">
+        <f>SUM(B24-'Table 26.2 sources'!I8)</f>
+        <v>1354470</v>
+      </c>
+      <c r="G25" t="s">
+        <v>126</v>
+      </c>
+      <c r="H25" s="5">
+        <f>SUM(H24-K15)</f>
+        <v>3050723</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>